--- a/output/pdf_financials_xlsx/FIN.xlsx
+++ b/output/pdf_financials_xlsx/FIN.xlsx
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.432151</v>
+        <v>-0.432151</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.59348</v>
+        <v>-0.59348</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-2.211569</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.432151</v>
+        <v>-0.432151</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.59348</v>
+        <v>-0.59348</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>-2.211569</v>
@@ -864,10 +864,10 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.432151</v>
+        <v>-0.432151</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.59348</v>
+        <v>-0.59348</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>-2.211569</v>
@@ -925,10 +925,10 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>-3.928645</v>
+        <v>3.928645</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-11.8696</v>
+        <v>11.8696</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>31.593843</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.432151</v>
+        <v>-0.432151</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.59348</v>
+        <v>-0.59348</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-2.211569</v>
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.432151</v>
+        <v>-0.432151</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.59348</v>
+        <v>-0.59348</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-2.211569</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0</v>
@@ -2201,16 +2201,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.313528</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.651323</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.026474</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.164003</v>
       </c>
     </row>
     <row r="93">
@@ -3396,7 +3396,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>-</t>
@@ -3714,7 +3718,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -3932,7 +3940,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" s="5" t="n">
         <v>0.313528</v>
       </c>
@@ -6259,10 +6271,10 @@
         </is>
       </c>
       <c r="F90" s="5" t="n">
-        <v>0.59348</v>
+        <v>-0.59348</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>2.211569</v>
+        <v>-2.211569</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -7190,10 +7202,10 @@
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>0.432151</v>
+        <v>-0.432151</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>0.59348</v>
+        <v>-0.59348</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/FIN.xlsx
+++ b/output/pdf_financials_xlsx/FIN.xlsx
@@ -645,10 +645,10 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-8.2e-05</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.017663</v>
       </c>
     </row>
     <row r="13">
@@ -952,10 +952,10 @@
         <v>-0.59348</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.211569</v>
+        <v>-2.211487</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2.011239</v>
+        <v>-1.993576</v>
       </c>
     </row>
     <row r="28">
@@ -990,10 +990,10 @@
         <v>-0.59348</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.211569</v>
+        <v>-2.211487</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.011239</v>
+        <v>-1.993576</v>
       </c>
     </row>
     <row r="30">
@@ -1083,16 +1083,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.576344</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.892711</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.74272</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.086317</v>
       </c>
     </row>
     <row r="35">
@@ -1121,16 +1121,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.576344</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.892711</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.74272</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.086317</v>
       </c>
     </row>
     <row r="37">
@@ -1349,16 +1349,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.576344</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.027395</v>
+        <v>0.134684</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.780468</v>
+        <v>0.037748</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.117877</v>
+        <v>0.03156</v>
       </c>
     </row>
     <row r="49">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -5172,7 +5172,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">

--- a/output/pdf_financials_xlsx/FIN.xlsx
+++ b/output/pdf_financials_xlsx/FIN.xlsx
@@ -4330,7 +4330,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
@@ -4654,7 +4658,11 @@
           <t>Shares issued for cash, net (Note 9)</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -4752,7 +4760,11 @@
           <t>Shares issued for cash, net</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E48" s="5" t="n">
         <v>0.858849</v>
       </c>
